--- a/documents/Yuma BW summary of events.xlsx
+++ b/documents/Yuma BW summary of events.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\D8000\MSCP\TempMSCP\D15-GenMonMgtNatFishPop\DataMgt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\BackwaterGenetics\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C83D81A-FA7A-410C-A153-C12ACB5FED84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3AA44AA-89A3-49DC-855D-A60DFC14AE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-330" yWindow="-21315" windowWidth="40080" windowHeight="20490" xr2:uid="{084E9E6E-4555-4D87-9DE7-6AB52ABD8AEB}"/>
+    <workbookView xWindow="-120" yWindow="0" windowWidth="21600" windowHeight="11295" xr2:uid="{084E9E6E-4555-4D87-9DE7-6AB52ABD8AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Yuma Cove BW" sheetId="1" r:id="rId1"/>
@@ -602,25 +602,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C823ABE2-FCC4-4918-916F-52ECD0D2A030}">
   <dimension ref="A1:R25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.44140625" customWidth="1"/>
-    <col min="6" max="6" width="8.109375" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" style="4" customWidth="1"/>
-    <col min="8" max="8" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.44140625" customWidth="1"/>
-    <col min="10" max="10" width="9.21875" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.44140625" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" customWidth="1"/>
+    <col min="10" max="10" width="9.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.42578125" customWidth="1"/>
     <col min="13" max="13" width="5" customWidth="1"/>
-    <col min="14" max="14" width="99.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="99.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="2" customFormat="1" ht="61.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" s="2" customFormat="1" ht="61.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -668,7 +668,7 @@
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>41316</v>
       </c>
@@ -685,7 +685,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>41591</v>
       </c>
@@ -720,7 +720,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>41592</v>
       </c>
@@ -743,7 +743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>41641</v>
       </c>
@@ -778,7 +778,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>41668</v>
       </c>
@@ -795,7 +795,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>42033</v>
       </c>
@@ -812,7 +812,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>42138</v>
       </c>
@@ -847,7 +847,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>42152</v>
       </c>
@@ -882,7 +882,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>42493</v>
       </c>
@@ -917,7 +917,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>42508</v>
       </c>
@@ -952,7 +952,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>42656</v>
       </c>
@@ -987,7 +987,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>42864</v>
       </c>
@@ -1022,7 +1022,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>43020</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>43385</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>43774</v>
       </c>
@@ -1127,7 +1127,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>43774</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>43775</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>43873</v>
       </c>
@@ -1218,7 +1218,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>44138</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>44498</v>
       </c>
@@ -1288,7 +1288,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>44867</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>45244</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>45587</v>
       </c>
@@ -1402,7 +1402,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>45674</v>
       </c>
@@ -1429,6 +1429,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0163b7c3-6fd4-4e9e-a0e0-ce73f2749c4b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d1e10837-682d-47d3-817a-d9a92e4874a6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CF451DEAB66511499DA003356CF88131" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2c5112bb62c158124ee29ce78bbce039">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0163b7c3-6fd4-4e9e-a0e0-ce73f2749c4b" xmlns:ns3="d1e10837-682d-47d3-817a-d9a92e4874a6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0436582cd0a4998eac3ca350cbb344ee" ns2:_="" ns3:_="">
     <xsd:import namespace="0163b7c3-6fd4-4e9e-a0e0-ce73f2749c4b"/>
@@ -1671,34 +1691,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0163b7c3-6fd4-4e9e-a0e0-ce73f2749c4b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="d1e10837-682d-47d3-817a-d9a92e4874a6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB9DB17A-C144-4024-A086-378C5372593F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8C3D921-06C9-4C7F-986E-BDAE29A3E88E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0163b7c3-6fd4-4e9e-a0e0-ce73f2749c4b"/>
+    <ds:schemaRef ds:uri="d1e10837-682d-47d3-817a-d9a92e4874a6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{795089E8-CACB-4891-89D5-050BE76B674C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{795089E8-CACB-4891-89D5-050BE76B674C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8C3D921-06C9-4C7F-986E-BDAE29A3E88E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB9DB17A-C144-4024-A086-378C5372593F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="0163b7c3-6fd4-4e9e-a0e0-ce73f2749c4b"/>
+    <ds:schemaRef ds:uri="d1e10837-682d-47d3-817a-d9a92e4874a6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>